--- a/Data/Home/Kitchen.AirQuality.xlsx
+++ b/Data/Home/Kitchen.AirQuality.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:I262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709270979</v>
+        <v>1711853593</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -497,10 +502,11 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709271624</v>
+        <v>1711860136</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -529,10 +535,11 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709280256</v>
+        <v>1711860722</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709288102</v>
+        <v>1711860998</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +601,15 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709232106</v>
+        <v>1711873970</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,10 +638,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +661,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709331238</v>
+        <v>1711877710</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -657,10 +671,15 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +698,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709331903</v>
+        <v>1711888484</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +712,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +731,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709332262</v>
+        <v>1711892988</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +741,11 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +764,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709337190</v>
+        <v>1711901281</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -753,10 +774,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +797,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709343835</v>
+        <v>1711928675</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -785,10 +807,11 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +830,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709349129</v>
+        <v>1711929853</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +844,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +863,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709355833</v>
+        <v>1711934379</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -849,10 +873,11 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +896,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709361249</v>
+        <v>1711943709</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -881,10 +906,11 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709368125</v>
+        <v>1712016033</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +943,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +962,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709404046</v>
+        <v>1712016767</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -945,10 +972,11 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +995,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709418122</v>
+        <v>1712017611</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +1005,15 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1032,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709418640</v>
+        <v>1712023552</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1046,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1065,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709419388</v>
+        <v>1712027899</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1041,10 +1075,11 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1098,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709423733</v>
+        <v>1712040683</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1073,10 +1108,11 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1131,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709430389</v>
+        <v>1712128695</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1145,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1164,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709441300</v>
+        <v>1712129489</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1178,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1197,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709457231</v>
+        <v>1712129652</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1169,10 +1207,15 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1234,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709486216</v>
+        <v>1712135364</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1201,10 +1244,11 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1267,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709503392</v>
+        <v>1712140600</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1281,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1300,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709504288</v>
+        <v>1712154259</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1265,10 +1310,11 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1333,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709504307</v>
+        <v>1712275311</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1297,10 +1343,11 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1366,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709509744</v>
+        <v>1712288429</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1329,10 +1376,11 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1399,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709519238</v>
+        <v>1712296458</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1413,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1432,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709536374</v>
+        <v>1712297201</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1393,10 +1442,11 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1465,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709605122</v>
+        <v>1712297612</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1425,10 +1475,15 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1502,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709606103</v>
+        <v>1712301151</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1516,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1535,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709624985</v>
+        <v>1712305627</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1549,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1568,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709655251</v>
+        <v>1712307848</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1521,10 +1578,11 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1601,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709689801</v>
+        <v>1712311531</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1615,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1634,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709690095</v>
+        <v>1712320331</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1644,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1667,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709691162</v>
+        <v>1712374763</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1677,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1700,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709703461</v>
+        <v>1712375936</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1714,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1733,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709714000</v>
+        <v>1712379764</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1747,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1766,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709749468</v>
+        <v>1712388240</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1776,11 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1799,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709772774</v>
+        <v>1712388299</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1745,10 +1809,15 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1836,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709772875</v>
+        <v>1712391880</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1850,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1869,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709774104</v>
+        <v>1712396584</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1879,11 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1902,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709785154</v>
+        <v>1712405893</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1841,10 +1912,11 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1935,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709785176</v>
+        <v>1712462138</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1945,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1968,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709792077</v>
+        <v>1712462860</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1982,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2001,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709798996</v>
+        <v>1712463531</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +2011,15 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2038,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709834907</v>
+        <v>1712472945</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1969,10 +2048,11 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2071,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709867093</v>
+        <v>1712475124</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2081,15 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2108,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709867162</v>
+        <v>1712478151</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2122,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2141,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709867680</v>
+        <v>1712482492</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2065,10 +2151,11 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2174,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709877364</v>
+        <v>1712494518</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2184,11 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2207,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709884843</v>
+        <v>1712495715</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2221,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2240,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709922667</v>
+        <v>1712496478</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2161,10 +2250,11 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2273,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709937136</v>
+        <v>1712503141</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2287,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2306,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709938026</v>
+        <v>1712511333</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2225,10 +2316,11 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2339,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709945092</v>
+        <v>1712534203</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2353,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2372,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709960826</v>
+        <v>1712534955</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2386,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2405,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709961386</v>
+        <v>1712535500</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2419,11 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2442,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709966424</v>
+        <v>1712540851</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2456,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2475,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709973187</v>
+        <v>1712545410</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2489,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2508,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710002306</v>
+        <v>1712553649</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2417,10 +2518,11 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2541,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710039706</v>
+        <v>1712556609</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2449,10 +2551,15 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2578,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710039970</v>
+        <v>1712558515</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2592,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2611,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710041232</v>
+        <v>1712561293</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2625,11 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2648,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710057286</v>
+        <v>1712567280</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2662,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2681,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710063806</v>
+        <v>1712571965</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2695,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2714,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710094037</v>
+        <v>1712580460</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2728,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2747,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710126315</v>
+        <v>1712620626</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2761,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2780,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710127219</v>
+        <v>1712621326</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2794,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2813,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710129046</v>
+        <v>1712621359</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2827,11 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2850,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710136581</v>
+        <v>1712625841</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2864,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2883,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710147346</v>
+        <v>1712630053</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2897,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2916,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710177338</v>
+        <v>1712638459</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2801,10 +2926,11 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2949,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710211227</v>
+        <v>1712652030</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2963,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2982,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710211944</v>
+        <v>1712660986</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2865,10 +2992,11 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3015,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710212327</v>
+        <v>1712726871</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2897,10 +3025,11 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3048,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710217626</v>
+        <v>1712727618</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3062,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3081,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710230242</v>
+        <v>1712728125</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3095,11 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3118,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710239057</v>
+        <v>1712734148</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3132,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3151,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710245492</v>
+        <v>1712738865</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3165,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3184,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710271834</v>
+        <v>1712751227</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3198,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3217,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710309183</v>
+        <v>1712792498</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3231,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3250,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710310105</v>
+        <v>1712793669</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3264,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3283,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710325227</v>
+        <v>1712797341</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3297,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3316,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710333831</v>
+        <v>1712806664</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3185,10 +3326,11 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3349,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710333839</v>
+        <v>1712812359</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3217,10 +3359,11 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3382,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710348414</v>
+        <v>1712812975</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3396,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3415,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710354898</v>
+        <v>1712813247</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3281,10 +3425,15 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3452,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710368123</v>
+        <v>1712817255</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3313,10 +3462,11 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3485,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710382122</v>
+        <v>1712822141</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3499,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3518,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710383038</v>
+        <v>1712831092</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3377,10 +3528,11 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3551,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710391520</v>
+        <v>1712879164</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3409,10 +3561,11 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3584,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710398653</v>
+        <v>1712879906</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3598,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3617,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710405731</v>
+        <v>1712880343</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3473,10 +3627,15 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3654,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710411980</v>
+        <v>1712885741</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3668,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3687,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710438614</v>
+        <v>1712890197</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3701,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3720,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710451337</v>
+        <v>1712899509</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3734,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3753,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710456811</v>
+        <v>1712900851</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3767,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3786,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710456911</v>
+        <v>1712901579</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3800,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3819,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710458527</v>
+        <v>1712901687</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3833,11 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3856,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710462794</v>
+        <v>1712906069</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3870,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3889,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710470037</v>
+        <v>1712908176</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3903,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3922,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710474721</v>
+        <v>1712920582</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3936,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3955,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710492428</v>
+        <v>1712920857</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3793,10 +3965,15 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3992,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710520473</v>
+        <v>1712925292</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3825,10 +4002,11 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4025,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710627816</v>
+        <v>1712929639</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +4039,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4058,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710628536</v>
+        <v>1712943887</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3889,10 +4068,11 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4091,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710628857</v>
+        <v>1712992741</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3921,10 +4101,11 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4124,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710634933</v>
+        <v>1712993488</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4138,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4157,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710655669</v>
+        <v>1712993570</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3985,10 +4167,15 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4194,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710665426</v>
+        <v>1712997720</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4208,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4227,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710665841</v>
+        <v>1713002225</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4049,10 +4237,11 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4260,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710671744</v>
+        <v>1713015699</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4081,10 +4270,11 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4293,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710694693</v>
+        <v>1713019989</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4307,7 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4326,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710710332</v>
+        <v>1713021147</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4145,10 +4336,11 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4359,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710731669</v>
+        <v>1713024677</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4373,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4392,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710732562</v>
+        <v>1713031488</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4209,10 +4402,11 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4425,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710732765</v>
+        <v>1713062005</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4241,10 +4435,11 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4458,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710742990</v>
+        <v>1713062777</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4472,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4491,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710750990</v>
+        <v>1713067074</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4305,10 +4501,15 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4528,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710783602</v>
+        <v>1713069889</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4337,10 +4538,11 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4561,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710800533</v>
+        <v>1713074086</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4575,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4594,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710800606</v>
+        <v>1713081012</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4608,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4627,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710801508</v>
+        <v>1713081432</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4641,11 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4664,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710808970</v>
+        <v>1713088976</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4678,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4697,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710823524</v>
+        <v>1713094485</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4497,10 +4707,15 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4734,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710827175</v>
+        <v>1713098953</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4748,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4767,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710842991</v>
+        <v>1713103740</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4781,7 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4800,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710875642</v>
+        <v>1713114162</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4593,10 +4810,11 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4833,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710896193</v>
+        <v>1713111157</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4847,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4866,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710897118</v>
+        <v>1713119127</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4657,10 +4876,11 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4899,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710897266</v>
+        <v>1713138935</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4689,10 +4909,11 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4932,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710909089</v>
+        <v>1713140099</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4946,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4965,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710929899</v>
+        <v>1713144504</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4979,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4998,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710932796</v>
+        <v>1713153013</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4785,10 +5008,11 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5031,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710932849</v>
+        <v>1713168224</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4817,10 +5041,11 @@
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5064,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710953399</v>
+        <v>1713168993</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5078,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5097,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710960294</v>
+        <v>1713179198</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5111,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5130,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710974011</v>
+        <v>1713191175</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5144,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5163,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710987402</v>
+        <v>1713245534</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5177,7 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5196,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710988300</v>
+        <v>1713245962</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5210,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5229,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710988386</v>
+        <v>1713246657</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5243,11 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5266,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710998508</v>
+        <v>1713254449</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5280,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5299,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710998523</v>
+        <v>1713263371</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5073,10 +5309,11 @@
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5332,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1711005478</v>
+        <v>1713272199</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5105,10 +5342,11 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5365,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1711013261</v>
+        <v>1713311777</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5379,7 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5398,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1711017725</v>
+        <v>1713312523</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5412,7 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5431,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1711017964</v>
+        <v>1713313443</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5445,11 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5468,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1711039732</v>
+        <v>1713319526</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5237,6 +5482,7 @@
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5501,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1711046694</v>
+        <v>1713324183</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5515,7 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5534,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1711064796</v>
+        <v>1713334219</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5297,10 +5544,11 @@
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5567,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1711076727</v>
+        <v>1713335132</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5329,10 +5577,15 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5604,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1711135364</v>
+        <v>1713343274</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5361,10 +5614,11 @@
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5637,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1711163171</v>
+        <v>1713348520</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5651,7 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5670,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1711163347</v>
+        <v>1713358857</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5425,10 +5680,11 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5703,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1711164433</v>
+        <v>1713423423</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5457,10 +5713,11 @@
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5736,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1711175855</v>
+        <v>1713423724</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5750,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5769,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1711182878</v>
+        <v>1713424662</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5521,10 +5779,15 @@
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5806,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1711214182</v>
+        <v>1713427837</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5553,10 +5816,11 @@
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5839,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1711234351</v>
+        <v>1713439897</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +5853,7 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5872,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1711235291</v>
+        <v>1713448905</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5617,10 +5882,11 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5905,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1711248639</v>
+        <v>1713484236</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5653,6 +5919,7 @@
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5938,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1711254253</v>
+        <v>1713485116</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +5952,7 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5971,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1711254733</v>
+        <v>1713494208</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5713,10 +5981,11 @@
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +6004,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1711266326</v>
+        <v>1713508094</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5745,10 +6014,11 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +6037,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1711273909</v>
+        <v>1713517966</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5781,6 +6051,7 @@
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +6070,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1711303925</v>
+        <v>1713518743</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5809,10 +6080,11 @@
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6103,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1711343647</v>
+        <v>1713518870</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5841,10 +6113,15 @@
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6140,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1711343719</v>
+        <v>1713523984</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5877,6 +6154,7 @@
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6173,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1711345340</v>
+        <v>1713528531</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5905,10 +6183,11 @@
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6206,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1711356934</v>
+        <v>1713537361</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5937,10 +6216,11 @@
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6239,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1711362248</v>
+        <v>1713584601</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5973,6 +6253,7 @@
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6272,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1711382470</v>
+        <v>1713585316</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6001,10 +6282,11 @@
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6305,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1711411553</v>
+        <v>1713586137</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6033,10 +6315,15 @@
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6342,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1711412081</v>
+        <v>1713592311</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6069,6 +6356,7 @@
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6375,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1711412579</v>
+        <v>1713596517</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6097,10 +6385,11 @@
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6408,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1711416752</v>
+        <v>1713601892</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6133,6 +6422,7 @@
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6441,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1711420964</v>
+        <v>1713610486</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6165,6 +6455,7 @@
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6474,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1711430047</v>
+        <v>1713619437</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6197,6 +6488,7 @@
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6507,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1711442341</v>
+        <v>1713630179</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6229,6 +6521,7 @@
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6540,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1711442669</v>
+        <v>1713630804</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6261,6 +6554,7 @@
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6573,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1711443962</v>
+        <v>1713631054</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6293,6 +6587,11 @@
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6610,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1711446912</v>
+        <v>1713629440</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6325,6 +6624,7 @@
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6643,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1711452091</v>
+        <v>1713633833</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6357,6 +6657,7 @@
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6676,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1711462328</v>
+        <v>1713642683</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6690,7 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6709,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1711515691</v>
+        <v>1713670890</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6421,6 +6723,7 @@
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6742,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1711524801</v>
+        <v>1713671909</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6453,6 +6756,7 @@
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6775,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1711526333</v>
+        <v>1713678995</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6485,6 +6789,11 @@
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6812,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1711530835</v>
+        <v>1713683272</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6517,6 +6826,7 @@
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6845,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1711539426</v>
+        <v>1713684139</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6545,10 +6855,15 @@
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +6882,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1711548560</v>
+        <v>1713688284</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6577,10 +6892,11 @@
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Excellent</t>
+          <t>Kitchen.AirQuality.state: Poor</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +6915,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1711610421</v>
+        <v>1713692988</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6613,6 +6929,7 @@
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +6948,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1711611157</v>
+        <v>1713706234</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6641,10 +6958,11 @@
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Poor</t>
+          <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +6981,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1711611990</v>
+        <v>1713711073</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6673,10 +6991,11 @@
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: SeverePollution</t>
+          <t>Kitchen.AirQuality.state: Good</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +7014,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1711619527</v>
+        <v>1713711828</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6709,6 +7028,7 @@
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +7047,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1711623809</v>
+        <v>1713712120</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6737,10 +7057,15 @@
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Kitchen.AirQuality.state: Good</t>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +7084,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1711633281</v>
+        <v>1713716499</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6769,10 +7094,2159 @@
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1713721018</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1713729629</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
           <t>Kitchen.AirQuality.state: Excellent</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1713829664</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>1713830431</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1713830831</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>1713836340</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>1713840813</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>1713852720</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>1713916573</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>1713917149</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>1713917471</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1713921609</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1713925747</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1713933775</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1713945715</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1713947105</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1713951376</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1713963442</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1714002770</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1714003493</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1714004197</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1714009703</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1714014143</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>1714024246</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>1714031378</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>1714035873</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>1714036177</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>1714041657</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>1714046481</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>1714055294</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>1714089040</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>1714090194</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>1714094519</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>1714103307</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>1714111059</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>1714111650</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>1714111967</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>1714115948</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>1714125315</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>1714134689</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>1714193192</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>1714203266</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>1714217676</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>1714226624</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>1714235390</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>1714236096</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>1714237166</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>1714235751</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>1714239661</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>1714247039</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>1714276724</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>1714277271</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>1714277648</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>1714280934</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>1714284970</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>1714287292</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>1714287345</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>1714290444</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>1714294480</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>1714300991</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>1714301503</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: SeverePollution</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>1714306688</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Poor</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>1714310879</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Good</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>AirQuality_Change</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>1714323934</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Kitchen.AirQuality.state: Excellent</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
